--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/8050-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/8050-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B67069E2-A819-46BF-AB8A-B68DF4518C82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CCF7E53B-F02E-41F1-903C-01B6620F952A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{52858782-6F01-4B0E-94F2-361C57B3CB42}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{653EE3BB-BAB4-4F8E-8D43-B26A61C470E7}"/>
   </bookViews>
   <sheets>
     <sheet name="8050-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1595,25 +1595,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{459A508F-B493-4F7A-A076-B904C4FD3DBF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B898B53C-FDCD-4173-952F-DF470780930D}">
   <dimension ref="A1:X43"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1647,7 +1646,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1683,7 +1682,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1735,7 +1734,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1803,7 +1802,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2024</v>
       </c>
@@ -1875,7 +1874,7 @@
         <v>7.58</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="39">
         <v>2023</v>
       </c>
@@ -1947,7 +1946,7 @@
         <v>6.16</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="37">
         <v>2022</v>
       </c>
@@ -2019,7 +2018,7 @@
         <v>7.9</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="39">
         <v>2021</v>
       </c>
@@ -2091,7 +2090,7 @@
         <v>5.73</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="37">
         <v>2020</v>
       </c>
@@ -2163,7 +2162,7 @@
         <v>5.37</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="39">
         <v>2019</v>
       </c>
@@ -2235,7 +2234,7 @@
         <v>6.69</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="37">
         <v>2018</v>
       </c>
@@ -2307,7 +2306,7 @@
         <v>5.22</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="39">
         <v>2017</v>
       </c>
@@ -2379,7 +2378,7 @@
         <v>8.0299999999999994</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="41">
         <v>2016</v>
       </c>
@@ -2451,7 +2450,7 @@
         <v>8.99</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="43"/>
       <c r="B14" s="44"/>
       <c r="C14" s="18" t="s">
@@ -2479,7 +2478,7 @@
       <c r="W14" s="52"/>
       <c r="X14" s="46"/>
     </row>
-    <row r="15" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="53">
         <v>2015</v>
       </c>
@@ -2551,7 +2550,7 @@
         <v>8.41</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="55"/>
       <c r="B16" s="56"/>
       <c r="C16" s="20" t="s">
@@ -2579,7 +2578,7 @@
       <c r="W16" s="62"/>
       <c r="X16" s="58"/>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="41">
         <v>2014</v>
       </c>
@@ -2651,7 +2650,7 @@
         <v>9.67</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="43"/>
       <c r="B18" s="44"/>
       <c r="C18" s="18" t="s">
@@ -2679,7 +2678,7 @@
       <c r="W18" s="52"/>
       <c r="X18" s="46"/>
     </row>
-    <row r="19" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="53">
         <v>2013</v>
       </c>
@@ -2751,7 +2750,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="55"/>
       <c r="B20" s="56"/>
       <c r="C20" s="20" t="s">
@@ -2779,7 +2778,7 @@
       <c r="W20" s="62"/>
       <c r="X20" s="58"/>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="41">
         <v>2012</v>
       </c>
@@ -2851,7 +2850,7 @@
         <v>9.65</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="43"/>
       <c r="B22" s="44"/>
       <c r="C22" s="18" t="s">
@@ -2879,7 +2878,7 @@
       <c r="W22" s="52"/>
       <c r="X22" s="46"/>
     </row>
-    <row r="23" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="53">
         <v>2011</v>
       </c>
@@ -2951,7 +2950,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="55"/>
       <c r="B24" s="56"/>
       <c r="C24" s="20" t="s">
@@ -2979,7 +2978,7 @@
       <c r="W24" s="62"/>
       <c r="X24" s="58"/>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="41">
         <v>2010</v>
       </c>
@@ -3051,7 +3050,7 @@
         <v>10.7</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="43"/>
       <c r="B26" s="44"/>
       <c r="C26" s="18" t="s">
@@ -3079,7 +3078,7 @@
       <c r="W26" s="52"/>
       <c r="X26" s="46"/>
     </row>
-    <row r="27" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="39">
         <v>2009</v>
       </c>
@@ -3151,7 +3150,7 @@
         <v>5.76</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="41">
         <v>2008</v>
       </c>
@@ -3223,7 +3222,7 @@
         <v>7.43</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="43"/>
       <c r="B29" s="44"/>
       <c r="C29" s="18" t="s">
@@ -3251,7 +3250,7 @@
       <c r="W29" s="52"/>
       <c r="X29" s="46"/>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="53">
         <v>2007</v>
       </c>
@@ -3323,7 +3322,7 @@
         <v>16.899999999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="55"/>
       <c r="B31" s="56"/>
       <c r="C31" s="20" t="s">
@@ -3351,7 +3350,7 @@
       <c r="W31" s="62"/>
       <c r="X31" s="58"/>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="41">
         <v>2006</v>
       </c>
@@ -3423,7 +3422,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="43"/>
       <c r="B33" s="44"/>
       <c r="C33" s="18" t="s">
@@ -3451,7 +3450,7 @@
       <c r="W33" s="52"/>
       <c r="X33" s="46"/>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="53">
         <v>2005</v>
       </c>
@@ -3523,7 +3522,7 @@
         <v>8.0500000000000007</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="55"/>
       <c r="B35" s="56"/>
       <c r="C35" s="20" t="s">
@@ -3551,7 +3550,7 @@
       <c r="W35" s="62"/>
       <c r="X35" s="58"/>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="41">
         <v>2004</v>
       </c>
@@ -3623,7 +3622,7 @@
         <v>8.81</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="43"/>
       <c r="B37" s="44"/>
       <c r="C37" s="18" t="s">
@@ -3651,7 +3650,7 @@
       <c r="W37" s="52"/>
       <c r="X37" s="46"/>
     </row>
-    <row r="38" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="53">
         <v>2003</v>
       </c>
@@ -3723,7 +3722,7 @@
         <v>9.68</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="55"/>
       <c r="B39" s="56"/>
       <c r="C39" s="20" t="s">
@@ -3751,7 +3750,7 @@
       <c r="W39" s="62"/>
       <c r="X39" s="58"/>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="37">
         <v>2002</v>
       </c>
@@ -3823,7 +3822,7 @@
         <v>4.24</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="39">
         <v>2001</v>
       </c>
@@ -3895,7 +3894,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="37">
         <v>2000</v>
       </c>
@@ -3967,7 +3966,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="39" t="s">
         <v>65</v>
       </c>
